--- a/Benchmark.xlsx
+++ b/Benchmark.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoeWe\IndProj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoeWe\Uni\IndProject\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F24FBFD-2072-431F-8CB0-C44D936F9597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1603B-2EA9-46CC-BD20-897368809B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{17CD3651-E119-4A47-BAB2-B543A6E028FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17CD3651-E119-4A47-BAB2-B543A6E028FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -416,10 +416,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A689574-C475-4B22-826E-7626F624CD40}">
-  <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -445,7 +445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -458,10 +458,6 @@
       <c r="D2">
         <v>60</v>
       </c>
-      <c r="E2">
-        <f>(ABS(B2-A2)+ABS(C2-A2)+ABS(D2-A2))/3</f>
-        <v>43.333333333333336</v>
-      </c>
       <c r="F2">
         <v>0</v>
       </c>
@@ -490,7 +486,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>30</v>
       </c>
@@ -503,10 +499,6 @@
       <c r="D3">
         <v>82</v>
       </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E13" si="0">(ABS(B3-A3)+ABS(C3-A3)+ABS(D3-A3))/3</f>
-        <v>50.333333333333336</v>
-      </c>
       <c r="F3">
         <v>50</v>
       </c>
@@ -535,7 +527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>60</v>
       </c>
@@ -548,10 +540,6 @@
       <c r="D4">
         <v>90</v>
       </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>30.666666666666668</v>
-      </c>
       <c r="F4">
         <v>88</v>
       </c>
@@ -580,7 +568,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>90</v>
       </c>
@@ -593,401 +581,998 @@
       <c r="D5">
         <v>120</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>121</v>
+      </c>
+      <c r="G5">
+        <v>112</v>
+      </c>
+      <c r="H5">
+        <v>110</v>
+      </c>
+      <c r="K5">
+        <v>96</v>
+      </c>
+      <c r="L5">
+        <v>72</v>
+      </c>
+      <c r="M5">
+        <v>76</v>
+      </c>
+      <c r="O5">
+        <v>92</v>
+      </c>
+      <c r="P5">
+        <v>66</v>
+      </c>
+      <c r="Q5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>120</v>
+      </c>
+      <c r="B6">
+        <v>174</v>
+      </c>
+      <c r="C6">
+        <v>124</v>
+      </c>
+      <c r="D6">
+        <v>127</v>
+      </c>
+      <c r="F6">
+        <v>144</v>
+      </c>
+      <c r="G6">
+        <v>146</v>
+      </c>
+      <c r="H6">
+        <v>156</v>
+      </c>
+      <c r="K6">
+        <v>90</v>
+      </c>
+      <c r="L6">
+        <v>95</v>
+      </c>
+      <c r="M6">
+        <v>98</v>
+      </c>
+      <c r="O6">
+        <v>110</v>
+      </c>
+      <c r="P6">
+        <v>106</v>
+      </c>
+      <c r="Q6">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>150</v>
+      </c>
+      <c r="B7">
+        <v>185</v>
+      </c>
+      <c r="C7">
+        <v>180</v>
+      </c>
+      <c r="D7">
+        <v>183</v>
+      </c>
+      <c r="F7">
+        <v>184</v>
+      </c>
+      <c r="G7">
+        <v>180</v>
+      </c>
+      <c r="H7">
+        <v>178</v>
+      </c>
+      <c r="K7">
+        <v>124</v>
+      </c>
+      <c r="L7">
+        <v>120</v>
+      </c>
+      <c r="M7">
+        <v>126</v>
+      </c>
+      <c r="O7">
+        <v>118</v>
+      </c>
+      <c r="P7">
+        <v>120</v>
+      </c>
+      <c r="Q7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>180</v>
+      </c>
+      <c r="B8">
+        <v>183</v>
+      </c>
+      <c r="C8">
+        <v>186</v>
+      </c>
+      <c r="D8">
+        <v>190</v>
+      </c>
+      <c r="F8">
+        <v>190</v>
+      </c>
+      <c r="G8">
+        <v>194</v>
+      </c>
+      <c r="H8">
+        <v>192</v>
+      </c>
+      <c r="K8">
+        <v>172</v>
+      </c>
+      <c r="L8">
+        <v>170</v>
+      </c>
+      <c r="M8">
+        <v>172</v>
+      </c>
+      <c r="O8">
+        <v>166</v>
+      </c>
+      <c r="P8">
+        <v>164</v>
+      </c>
+      <c r="Q8">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>210</v>
+      </c>
+      <c r="B9">
+        <v>246</v>
+      </c>
+      <c r="C9">
+        <v>255</v>
+      </c>
+      <c r="D9">
+        <v>254</v>
+      </c>
+      <c r="F9">
+        <v>256</v>
+      </c>
+      <c r="G9">
+        <v>245</v>
+      </c>
+      <c r="H9">
+        <v>259</v>
+      </c>
+      <c r="K9">
+        <v>198</v>
+      </c>
+      <c r="L9">
+        <v>200</v>
+      </c>
+      <c r="M9">
+        <v>199</v>
+      </c>
+      <c r="O9">
+        <v>198</v>
+      </c>
+      <c r="P9">
+        <v>196</v>
+      </c>
+      <c r="Q9">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>240</v>
+      </c>
+      <c r="B10">
+        <v>276</v>
+      </c>
+      <c r="C10">
+        <v>271</v>
+      </c>
+      <c r="D10">
+        <v>274</v>
+      </c>
+      <c r="F10">
+        <v>240</v>
+      </c>
+      <c r="G10">
+        <v>244</v>
+      </c>
+      <c r="H10">
+        <v>248</v>
+      </c>
+      <c r="K10">
+        <v>222</v>
+      </c>
+      <c r="L10">
+        <v>224</v>
+      </c>
+      <c r="M10">
+        <v>222</v>
+      </c>
+      <c r="O10">
+        <v>200</v>
+      </c>
+      <c r="P10">
+        <v>224</v>
+      </c>
+      <c r="Q10">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>270</v>
+      </c>
+      <c r="B11">
+        <v>286</v>
+      </c>
+      <c r="C11">
+        <v>279</v>
+      </c>
+      <c r="D11">
+        <v>271</v>
+      </c>
+      <c r="F11">
+        <v>264</v>
+      </c>
+      <c r="G11">
+        <v>257</v>
+      </c>
+      <c r="H11">
+        <v>270</v>
+      </c>
+      <c r="K11">
+        <v>255</v>
+      </c>
+      <c r="L11">
+        <v>248</v>
+      </c>
+      <c r="M11">
+        <v>250</v>
+      </c>
+      <c r="O11">
+        <v>246</v>
+      </c>
+      <c r="P11">
+        <v>248</v>
+      </c>
+      <c r="Q11">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>300</v>
+      </c>
+      <c r="B12">
+        <v>277</v>
+      </c>
+      <c r="C12">
+        <v>345</v>
+      </c>
+      <c r="D12">
+        <v>347</v>
+      </c>
+      <c r="F12">
+        <v>304</v>
+      </c>
+      <c r="G12">
+        <v>318</v>
+      </c>
+      <c r="H12">
+        <v>327</v>
+      </c>
+      <c r="K12">
+        <v>276</v>
+      </c>
+      <c r="L12">
+        <v>278</v>
+      </c>
+      <c r="M12">
+        <v>277</v>
+      </c>
+      <c r="O12">
+        <v>276</v>
+      </c>
+      <c r="P12">
+        <v>286</v>
+      </c>
+      <c r="Q12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>330</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>354</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>348</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>314</v>
+      </c>
+      <c r="L13">
+        <v>310</v>
+      </c>
+      <c r="M13">
+        <v>314</v>
+      </c>
+      <c r="O13">
+        <v>308</v>
+      </c>
+      <c r="P13">
+        <v>312</v>
+      </c>
+      <c r="Q13">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f>MIN(ABS(B2-A2), 360-ABS(B2-A2))</f>
+        <v>30</v>
+      </c>
+      <c r="C15">
+        <f>MIN(ABS(C2-A2), 360-ABS(C2-A2))</f>
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <f>MIN(ABS(D2-A2), 360-ABS(D2-A2))</f>
+        <v>60</v>
+      </c>
+      <c r="F15">
+        <f>MIN(ABS(F2-A2), 360-ABS(F2-A2))</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f>MIN(ABS(G2-A2), 360-ABS(G2-A2))</f>
+        <v>34</v>
+      </c>
+      <c r="H15">
+        <f>MIN(ABS(H2-A2), 360-ABS(H2-A2))</f>
+        <v>36</v>
+      </c>
+      <c r="K15">
+        <f>MIN(ABS(K2-A2), 360-ABS(K2-A2))</f>
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <f>MIN(ABS(L2-A2), 360-ABS(L2-A2))</f>
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <f>MIN(ABS(M2-A2), 360-ABS(M2-A2))</f>
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <f>MIN(ABS(O2-A2), 360-ABS(O2-A2))</f>
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <f>MIN(ABS(P2-A2), 360-ABS(P2-A2))</f>
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <f>MIN(ABS(Q2-A2), 360-ABS(Q2-A2))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" ref="B16:B26" si="0">MIN(ABS(B3-A3), 360-ABS(B3-A3))</f>
+        <v>45</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:C26" si="1">MIN(ABS(C3-A3), 360-ABS(C3-A3))</f>
+        <v>54</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ref="D16:D26" si="2">MIN(ABS(D3-A3), 360-ABS(D3-A3))</f>
+        <v>52</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ref="F16:F26" si="3">MIN(ABS(F3-A3), 360-ABS(F3-A3))</f>
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ref="G16:G26" si="4">MIN(ABS(G3-A3), 360-ABS(G3-A3))</f>
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ref="H16:H26" si="5">MIN(ABS(H3-A3), 360-ABS(H3-A3))</f>
+        <v>18</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ref="K16:K26" si="6">MIN(ABS(K3-A3), 360-ABS(K3-A3))</f>
+        <v>8</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ref="L16:L26" si="7">MIN(ABS(L3-A3), 360-ABS(L3-A3))</f>
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ref="M16:M26" si="8">MIN(ABS(M3-A3), 360-ABS(M3-A3))</f>
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <f t="shared" ref="O16:O26" si="9">MIN(ABS(O3-A3), 360-ABS(O3-A3))</f>
+        <v>14</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ref="P16:P26" si="10">MIN(ABS(P3-A3), 360-ABS(P3-A3))</f>
+        <v>8</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" ref="Q16:Q26" si="11">MIN(ABS(Q3-A3), 360-ABS(Q3-A3))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="9"/>
+        <v>32</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="9"/>
+        <v>14</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="9"/>
+        <v>12</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="9"/>
+        <v>24</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="10"/>
+        <v>22</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F5">
-        <v>121</v>
-      </c>
-      <c r="G5">
-        <v>112</v>
-      </c>
-      <c r="H5">
-        <v>110</v>
-      </c>
-      <c r="K5">
-        <v>96</v>
-      </c>
-      <c r="L5">
-        <v>72</v>
-      </c>
-      <c r="M5">
-        <v>76</v>
-      </c>
-      <c r="O5">
-        <v>92</v>
-      </c>
-      <c r="P5">
-        <v>66</v>
-      </c>
-      <c r="Q5">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>120</v>
-      </c>
-      <c r="B6">
-        <v>174</v>
-      </c>
-      <c r="C6">
-        <v>124</v>
-      </c>
-      <c r="D6">
-        <v>127</v>
-      </c>
-      <c r="E6">
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="5"/>
+        <v>27</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="9"/>
+        <v>24</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26">
         <f t="shared" si="0"/>
-        <v>21.666666666666668</v>
-      </c>
-      <c r="F6">
-        <v>144</v>
-      </c>
-      <c r="G6">
-        <v>146</v>
-      </c>
-      <c r="H6">
-        <v>156</v>
-      </c>
-      <c r="K6">
-        <v>90</v>
-      </c>
-      <c r="L6">
-        <v>95</v>
-      </c>
-      <c r="M6">
-        <v>98</v>
-      </c>
-      <c r="O6">
-        <v>110</v>
-      </c>
-      <c r="P6">
-        <v>106</v>
-      </c>
-      <c r="Q6">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>150</v>
-      </c>
-      <c r="B7">
-        <v>185</v>
-      </c>
-      <c r="C7">
-        <v>180</v>
-      </c>
-      <c r="D7">
-        <v>183</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>32.666666666666664</v>
-      </c>
-      <c r="F7">
-        <v>184</v>
-      </c>
-      <c r="G7">
-        <v>180</v>
-      </c>
-      <c r="H7">
-        <v>178</v>
-      </c>
-      <c r="K7">
-        <v>124</v>
-      </c>
-      <c r="L7">
-        <v>120</v>
-      </c>
-      <c r="M7">
-        <v>126</v>
-      </c>
-      <c r="O7">
-        <v>118</v>
-      </c>
-      <c r="P7">
-        <v>120</v>
-      </c>
-      <c r="Q7">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>180</v>
-      </c>
-      <c r="B8">
-        <v>183</v>
-      </c>
-      <c r="C8">
-        <v>186</v>
-      </c>
-      <c r="D8">
-        <v>190</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>6.333333333333333</v>
-      </c>
-      <c r="F8">
-        <v>190</v>
-      </c>
-      <c r="G8">
-        <v>194</v>
-      </c>
-      <c r="H8">
-        <v>192</v>
-      </c>
-      <c r="K8">
-        <v>172</v>
-      </c>
-      <c r="L8">
-        <v>170</v>
-      </c>
-      <c r="M8">
-        <v>172</v>
-      </c>
-      <c r="O8">
-        <v>166</v>
-      </c>
-      <c r="P8">
-        <v>164</v>
-      </c>
-      <c r="Q8">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <v>210</v>
-      </c>
-      <c r="B9">
-        <v>246</v>
-      </c>
-      <c r="C9">
-        <v>255</v>
-      </c>
-      <c r="D9">
-        <v>254</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>41.666666666666664</v>
-      </c>
-      <c r="F9">
-        <v>256</v>
-      </c>
-      <c r="G9">
-        <v>245</v>
-      </c>
-      <c r="H9">
-        <v>259</v>
-      </c>
-      <c r="K9">
-        <v>198</v>
-      </c>
-      <c r="L9">
-        <v>200</v>
-      </c>
-      <c r="M9">
-        <v>199</v>
-      </c>
-      <c r="O9">
-        <v>198</v>
-      </c>
-      <c r="P9">
-        <v>196</v>
-      </c>
-      <c r="Q9">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>240</v>
-      </c>
-      <c r="B10">
-        <v>276</v>
-      </c>
-      <c r="C10">
-        <v>271</v>
-      </c>
-      <c r="D10">
-        <v>274</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>33.666666666666664</v>
-      </c>
-      <c r="F10">
-        <v>240</v>
-      </c>
-      <c r="G10">
-        <v>244</v>
-      </c>
-      <c r="H10">
-        <v>248</v>
-      </c>
-      <c r="K10">
-        <v>222</v>
-      </c>
-      <c r="L10">
-        <v>224</v>
-      </c>
-      <c r="M10">
-        <v>222</v>
-      </c>
-      <c r="O10">
-        <v>200</v>
-      </c>
-      <c r="P10">
-        <v>224</v>
-      </c>
-      <c r="Q10">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>270</v>
-      </c>
-      <c r="B11">
-        <v>286</v>
-      </c>
-      <c r="C11">
-        <v>279</v>
-      </c>
-      <c r="D11">
-        <v>271</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>8.6666666666666661</v>
-      </c>
-      <c r="F11">
-        <v>264</v>
-      </c>
-      <c r="G11">
-        <v>257</v>
-      </c>
-      <c r="H11">
-        <v>270</v>
-      </c>
-      <c r="K11">
-        <v>255</v>
-      </c>
-      <c r="L11">
-        <v>248</v>
-      </c>
-      <c r="M11">
-        <v>250</v>
-      </c>
-      <c r="O11">
-        <v>246</v>
-      </c>
-      <c r="P11">
-        <v>248</v>
-      </c>
-      <c r="Q11">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>300</v>
-      </c>
-      <c r="B12">
-        <v>277</v>
-      </c>
-      <c r="C12">
-        <v>345</v>
-      </c>
-      <c r="D12">
-        <v>347</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>38.333333333333336</v>
-      </c>
-      <c r="F12">
-        <v>304</v>
-      </c>
-      <c r="G12">
-        <v>318</v>
-      </c>
-      <c r="H12">
-        <v>327</v>
-      </c>
-      <c r="K12">
-        <v>276</v>
-      </c>
-      <c r="L12">
-        <v>278</v>
-      </c>
-      <c r="M12">
-        <v>277</v>
-      </c>
-      <c r="O12">
-        <v>276</v>
-      </c>
-      <c r="P12">
-        <v>286</v>
-      </c>
-      <c r="Q12">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>330</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>354</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>226.66666666666666</v>
-      </c>
-      <c r="F13">
-        <v>348</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="K13">
-        <v>314</v>
-      </c>
-      <c r="L13">
-        <v>310</v>
-      </c>
-      <c r="M13">
-        <v>314</v>
-      </c>
-      <c r="O13">
-        <v>308</v>
-      </c>
-      <c r="P13">
-        <v>312</v>
-      </c>
-      <c r="Q13">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>360</v>
+        <v>30</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="5"/>
+        <v>32</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <f>MAX(B15:D26)</f>
+        <v>60</v>
+      </c>
+      <c r="D27">
+        <f>AVERAGE(B15:D26)</f>
+        <v>29.972222222222221</v>
+      </c>
+      <c r="E27">
+        <f>_xlfn.STDEV.S(B15:D26)</f>
+        <v>15.708934875434265</v>
+      </c>
+      <c r="H27">
+        <f>AVERAGE(F15:H26)</f>
+        <v>21.694444444444443</v>
+      </c>
+      <c r="I27">
+        <f>_xlfn.STDEV.S(F15:H26)</f>
+        <v>12.770097760996071</v>
+      </c>
+      <c r="M27">
+        <f>AVERAGE(K15:M26)</f>
+        <v>15.972222222222221</v>
+      </c>
+      <c r="N27">
+        <f>_xlfn.STDEV.S(K15:M26)</f>
+        <v>6.8888568867664262</v>
+      </c>
+      <c r="Q27">
+        <f>AVERAGE(O15:Q26)</f>
+        <v>17.361111111111111</v>
+      </c>
+      <c r="R27">
+        <f>_xlfn.STDEV.S(O15:Q26)</f>
+        <v>8.7346691090415334</v>
       </c>
     </row>
   </sheetData>
